--- a/data/trans_orig/IP3102-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3102-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17942</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>28050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25171</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>31163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49206</t>
+          <t>49140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40888</t>
+          <t>41750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>49662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69889</t>
+          <t>70079</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18025</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>36302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>28633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>34665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18795</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>35238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41425</t>
+          <t>41073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>64053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53057</t>
+          <t>52719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76583</t>
+          <t>74525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>89118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120453</t>
+          <t>118514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>149070</t>
+          <t>151096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186521</t>
+          <t>187810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132336</t>
+          <t>133403</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164317</t>
+          <t>164053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>154484</t>
+          <t>157708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187641</t>
+          <t>190810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>300360</t>
+          <t>298184</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>343416</t>
+          <t>342356</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85127</t>
+          <t>84151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113513</t>
+          <t>112159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79642</t>
+          <t>79260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107582</t>
+          <t>106180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172472</t>
+          <t>171688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210942</t>
+          <t>208902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43699</t>
+          <t>44792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64597</t>
+          <t>66470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43157</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64747</t>
+          <t>64404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93293</t>
+          <t>91870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123442</t>
+          <t>123018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22146</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>30718</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40162</t>
+          <t>39489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>61642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54664</t>
+          <t>55280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75579</t>
+          <t>75076</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>45052</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64220</t>
+          <t>63402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106559</t>
+          <t>104965</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>132311</t>
+          <t>132288</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43245</t>
+          <t>43827</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32160</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>50091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63187</t>
+          <t>63759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87169</t>
+          <t>87131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>16858</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>30360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26253</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52080</t>
+          <t>52387</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53628</t>
+          <t>53690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55194</t>
+          <t>55088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71038</t>
+          <t>71460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101862</t>
+          <t>100184</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97230</t>
+          <t>96656</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>127570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130300</t>
+          <t>127989</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>166210</t>
+          <t>164617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>234419</t>
+          <t>233646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280648</t>
+          <t>279358</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>225609</t>
+          <t>227257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>266540</t>
+          <t>266659</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>231253</t>
+          <t>232246</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>275422</t>
+          <t>275821</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>473039</t>
+          <t>470924</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>528001</t>
+          <t>526941</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131988</t>
+          <t>132657</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>167528</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129561</t>
+          <t>129600</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>163557</t>
+          <t>162013</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>269487</t>
+          <t>269884</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>319960</t>
+          <t>319149</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74750</t>
+          <t>76187</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101520</t>
+          <t>103828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69813</t>
+          <t>69160</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96400</t>
+          <t>97677</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150552</t>
+          <t>151812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>190438</t>
+          <t>189648</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>14213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26862</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>17596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31307</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34496</t>
+          <t>35365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52851</t>
+          <t>55166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>18787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>32935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>22211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>36878</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>45241</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65300</t>
+          <t>64564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32415</t>
+          <t>33575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18598</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43461</t>
+          <t>42731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21185</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24624</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>23686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>41820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66394</t>
+          <t>64703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91755</t>
+          <t>91985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87298</t>
+          <t>87226</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116936</t>
+          <t>115393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161013</t>
+          <t>158551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198213</t>
+          <t>198483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126378</t>
+          <t>125574</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158467</t>
+          <t>158113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114581</t>
+          <t>114801</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146761</t>
+          <t>145997</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>248692</t>
+          <t>250859</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>293237</t>
+          <t>296367</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62483</t>
+          <t>62421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>86949</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68714</t>
+          <t>67236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95575</t>
+          <t>94958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136009</t>
+          <t>136889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175522</t>
+          <t>172600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89490</t>
+          <t>91035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118349</t>
+          <t>120070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102238</t>
+          <t>101635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133472</t>
+          <t>133464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201454</t>
+          <t>201061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243383</t>
+          <t>244841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36253</t>
+          <t>35507</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>42980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64736</t>
+          <t>63440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30935</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42856</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61197</t>
+          <t>61535</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>78841</t>
+          <t>78354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>104848</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31236</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34030</t>
+          <t>33893</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37700</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58321</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50065</t>
+          <t>51150</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>72196</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39957</t>
+          <t>39299</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59541</t>
+          <t>58853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95425</t>
+          <t>95537</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124153</t>
+          <t>123526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38972</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62983</t>
+          <t>63710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>108234</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142320</t>
+          <t>142094</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134222</t>
+          <t>132419</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170449</t>
+          <t>168510</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>251686</t>
+          <t>251626</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>301572</t>
+          <t>299891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>188382</t>
+          <t>187137</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>227391</t>
+          <t>226750</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>193083</t>
+          <t>195115</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>232513</t>
+          <t>233817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>392800</t>
+          <t>393548</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>450341</t>
+          <t>447097</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95442</t>
+          <t>96802</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127675</t>
+          <t>126998</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>100942</t>
+          <t>100294</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132208</t>
+          <t>131800</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>204113</t>
+          <t>206642</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251007</t>
+          <t>251501</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>169007</t>
+          <t>167508</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206797</t>
+          <t>205638</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161988</t>
+          <t>161155</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>199355</t>
+          <t>198739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>340197</t>
+          <t>341631</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>396063</t>
+          <t>392844</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>23531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21698</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36251</t>
+          <t>35479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>28441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27341</t>
+          <t>26915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>36723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>42004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59319</t>
+          <t>59034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>19296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36157</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38622</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61190</t>
+          <t>59895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65856</t>
+          <t>65746</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91659</t>
+          <t>90964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59872</t>
+          <t>59647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85611</t>
+          <t>86526</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133286</t>
+          <t>134515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168372</t>
+          <t>170215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91606</t>
+          <t>92227</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121011</t>
+          <t>121405</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104879</t>
+          <t>105343</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138317</t>
+          <t>136526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>205012</t>
+          <t>206350</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>248680</t>
+          <t>250226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82216</t>
+          <t>80951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109896</t>
+          <t>109603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88565</t>
+          <t>90274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118700</t>
+          <t>119564</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180767</t>
+          <t>180631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220109</t>
+          <t>221327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124484</t>
+          <t>123866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>156249</t>
+          <t>155037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118714</t>
+          <t>121195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153647</t>
+          <t>153228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250914</t>
+          <t>253203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296708</t>
+          <t>297626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34499</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55597</t>
+          <t>57230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34756</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52986</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28580</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67554</t>
+          <t>68261</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92276</t>
+          <t>92771</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48480</t>
+          <t>48550</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34333</t>
+          <t>33211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52342</t>
+          <t>52684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70764</t>
+          <t>69647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95871</t>
+          <t>96104</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37355</t>
+          <t>37678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55854</t>
+          <t>55949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47935</t>
+          <t>48608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68836</t>
+          <t>69113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>92169</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119954</t>
+          <t>118757</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38022</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>50388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>54673</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81446</t>
+          <t>80574</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94334</t>
+          <t>94474</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126790</t>
+          <t>125340</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>86202</t>
+          <t>84412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115603</t>
+          <t>114874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>187369</t>
+          <t>188046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233575</t>
+          <t>231128</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>144030</t>
+          <t>143910</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180718</t>
+          <t>180375</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153954</t>
+          <t>154622</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190250</t>
+          <t>192230</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>307403</t>
+          <t>306613</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>359559</t>
+          <t>361253</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>127943</t>
+          <t>128768</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>163555</t>
+          <t>163144</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>138435</t>
+          <t>139191</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178121</t>
+          <t>175069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>279093</t>
+          <t>279524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>328278</t>
+          <t>329100</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>185992</t>
+          <t>187938</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>225191</t>
+          <t>226371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>204427</t>
+          <t>205997</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>245682</t>
+          <t>245394</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>402280</t>
+          <t>403639</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>459367</t>
+          <t>459626</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
